--- a/results/AIC.xlsx
+++ b/results/AIC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blackmon/Desktop/github/CURE-chromosome-number/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{916BD326-574E-5A44-BF40-5D4B404FC1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{1C669C56-045E-9044-9B3F-4B0759E99AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="45420" yWindow="-940" windowWidth="28040" windowHeight="17440" xr2:uid="{F93F5B04-2B2C-B041-A1EA-EEE9D1486963}"/>
   </bookViews>
@@ -179,7 +179,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -314,8 +314,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -493,6 +500,18 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -656,8 +675,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1035,6 +1058,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B673241-7D8F-1441-8C53-E1AE90602CD0}">
   <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1066,24 +1092,24 @@
       <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>237.14635000000001</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="3">
         <v>182.42615000000001</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>201.17778000000001</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="3">
         <v>180.42615000000001</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>232.72353000000001</v>
       </c>
     </row>
@@ -1091,7 +1117,7 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>2453.3422300000002</v>
       </c>
       <c r="C4">
@@ -1117,7 +1143,7 @@
       <c r="D5">
         <v>498.84998000000002</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>496.10383999999999</v>
       </c>
     </row>
@@ -1125,7 +1151,7 @@
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>16489.378939999999</v>
       </c>
       <c r="C6">
@@ -1142,7 +1168,7 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>193.95703</v>
       </c>
       <c r="C7">
@@ -1159,7 +1185,7 @@
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>8143.2707899999996</v>
       </c>
       <c r="C8">
@@ -1176,7 +1202,7 @@
       <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>1073.85571</v>
       </c>
       <c r="C9">
@@ -1190,19 +1216,19 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="3">
         <v>363.19900000000001</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="3">
         <v>361.42248000000001</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>366.61716999999999</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <v>369.41982000000002</v>
       </c>
     </row>
@@ -1210,7 +1236,7 @@
       <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>423.82387</v>
       </c>
       <c r="C11">
@@ -1230,7 +1256,7 @@
       <c r="B12">
         <v>373.33613000000003</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>367.17273999999998</v>
       </c>
       <c r="D12">
@@ -1253,24 +1279,24 @@
       <c r="D13" t="s">
         <v>6</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>20.943619999999999</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="3">
         <v>708.96788000000004</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="3">
         <v>706.96788000000004</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>736.96371999999997</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2">
         <v>732.42286000000001</v>
       </c>
     </row>
@@ -1278,7 +1304,7 @@
       <c r="A15" t="s">
         <v>19</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>809.05614000000003</v>
       </c>
       <c r="C15">
@@ -1292,36 +1318,36 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="3">
         <v>226.91046</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="3">
         <v>225.48236</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>257.68007999999998</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2">
         <v>255.69686999999999</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="A17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="3">
         <v>584.04661999999996</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2">
         <v>591.63073999999995</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="3">
         <v>582.04661999999996</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="2">
         <v>615.96361999999999</v>
       </c>
     </row>
@@ -1329,7 +1355,7 @@
       <c r="A18" t="s">
         <v>22</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="1">
         <v>144.45386999999999</v>
       </c>
       <c r="C18">
@@ -1346,7 +1372,7 @@
       <c r="A19" t="s">
         <v>23</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="1">
         <v>573.33563000000004</v>
       </c>
       <c r="C19">
@@ -1360,36 +1386,36 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="A20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="3">
         <v>527.80457999999999</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="3">
         <v>525.80457999999999</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="2">
         <v>541.66656</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="2">
         <v>539.66656</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="A21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="3">
         <v>108.13646</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="2">
         <v>114.77994</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="3">
         <v>106.13646</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="2">
         <v>132.28551999999999</v>
       </c>
     </row>
@@ -1397,7 +1423,7 @@
       <c r="A22" t="s">
         <v>26</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="1">
         <v>5946.3493200000003</v>
       </c>
       <c r="C22">
@@ -1411,87 +1437,87 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="A23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="3">
         <v>215.32107999999999</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="2">
         <v>213.32107999999999</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="2">
         <v>213.32107999999999</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="3">
         <v>211.32107999999999</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="A24" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="4">
         <v>280.77733000000001</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="4">
         <v>316.95668000000001</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="A25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="3">
         <v>268.65926000000002</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="3">
         <v>269.60678999999999</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="2">
         <v>349.36299000000002</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="A26" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="3">
         <v>233.55376999999999</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="3">
         <v>231.55376999999999</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="3">
         <v>230.08964</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="2">
         <v>238.39759000000001</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="A27" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="3">
         <v>56.447139999999997</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="3">
         <v>54.447139999999997</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="2">
         <v>59.583930000000002</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="2">
         <v>61.543759999999999</v>
       </c>
     </row>
@@ -1499,7 +1525,7 @@
       <c r="A28" t="s">
         <v>32</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="1">
         <v>1858.07331</v>
       </c>
       <c r="C28">
@@ -1516,7 +1542,7 @@
       <c r="A29" t="s">
         <v>33</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="1">
         <v>1307.7874200000001</v>
       </c>
       <c r="C29">
@@ -1533,7 +1559,7 @@
       <c r="A30" t="s">
         <v>34</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="1">
         <v>2182.4754699999999</v>
       </c>
       <c r="C30">
@@ -1550,7 +1576,7 @@
       <c r="A31" t="s">
         <v>35</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="1">
         <v>119.25664</v>
       </c>
       <c r="C31">
@@ -1567,10 +1593,10 @@
       <c r="A32" t="s">
         <v>36</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="1">
         <v>106.44583</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="1">
         <v>104.44583</v>
       </c>
       <c r="D32">
@@ -1584,16 +1610,16 @@
       <c r="A33" t="s">
         <v>37</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="1">
         <v>332.51035000000002</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="1">
         <v>332.76251000000002</v>
       </c>
       <c r="D33">
         <v>336.79833000000002</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="1">
         <v>334.79833000000002</v>
       </c>
     </row>
@@ -1604,7 +1630,7 @@
       <c r="B34" t="s">
         <v>6</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="1">
         <v>73.343379999999996</v>
       </c>
       <c r="D34" t="s">
@@ -1618,7 +1644,7 @@
       <c r="A35" t="s">
         <v>39</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="1">
         <v>98.134519999999995</v>
       </c>
       <c r="C35">
